--- a/output/pdf_financials_xlsx/TTG.xlsx
+++ b/output/pdf_financials_xlsx/TTG.xlsx
@@ -6225,19 +6225,19 @@
         <v>0.120259</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.010299</v>
+        <v>0.345334</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.024882</v>
+        <v>0.462324</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.079655</v>
+        <v>0.640436</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.217962</v>
+        <v>0.425932</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.726859</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -6255,22 +6255,22 @@
         <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.499708</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.195042</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.195042</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.411046</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.649565</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.649565</v>
       </c>
     </row>
     <row r="93">
@@ -10057,7 +10057,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10787,7 +10791,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -12836,7 +12844,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TTG.xlsx
+++ b/output/pdf_financials_xlsx/TTG.xlsx
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001081</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>3.5e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.157797</v>
+        <v>-0.158878</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.608897</v>
+        <v>-0.608932</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.079253</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.157797</v>
+        <v>-0.158878</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.608897</v>
+        <v>-0.608932</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.293694</v>
@@ -2650,55 +2650,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.138184</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.363402</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.429097</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.320267</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.26241</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.182822</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.045538</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.013611</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.039327</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.16977</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.03199</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001222</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.473014</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.09517200000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.432235</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.478689</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.330477</v>
       </c>
     </row>
     <row r="35">
@@ -2766,55 +2766,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.138184</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.363402</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.429097</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.320267</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.26241</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.182822</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.045538</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.013611</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.039327</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.16977</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.03199</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001222</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.473014</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.09517200000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.432235</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.478689</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.330477</v>
       </c>
     </row>
     <row r="37">
@@ -3462,55 +3462,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.139867</v>
+        <v>0.001683</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.371085</v>
+        <v>0.007683</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.44436</v>
+        <v>0.015263</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.32995</v>
+        <v>0.009683000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.272093</v>
+        <v>0.009683000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.203467</v>
+        <v>0.020645</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.046866</v>
+        <v>0.001328</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.014939</v>
+        <v>0.001328</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.040651</v>
+        <v>0.001324</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.16977</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.03199</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.001222</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.473832</v>
+        <v>0.000818</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.104803</v>
+        <v>0.009631000000000001</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.443426</v>
+        <v>0.011191</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.492035</v>
+        <v>0.013346</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.344935</v>
+        <v>0.014458</v>
       </c>
     </row>
     <row r="49">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E272" s="5" t="n">
